--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,12 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109171</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549788.3990509292</v>
+        <v>549788</v>
       </c>
       <c r="R3" t="n">
-        <v>6408425.300940051</v>
+        <v>6408425</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,19 +864,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -925,12 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99805</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549591.2590261507</v>
+        <v>549591</v>
       </c>
       <c r="R4" t="n">
-        <v>6408223.075239697</v>
+        <v>6408223</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -995,19 +975,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1051,12 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549788.3990509292</v>
+        <v>549788</v>
       </c>
       <c r="R5" t="n">
-        <v>6408425.300940051</v>
+        <v>6408425</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,19 +1082,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99805</v>
+        <v>99810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104061</v>
+        <v>104070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99810</v>
+        <v>99811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104070</v>
+        <v>104073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99811</v>
+        <v>99838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99838</v>
+        <v>99844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104100</v>
+        <v>104106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99844</v>
+        <v>99851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104106</v>
+        <v>104113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99851</v>
+        <v>99855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99855</v>
+        <v>99862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104117</v>
+        <v>104124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99865</v>
+        <v>99870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104127</v>
+        <v>104132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99870</v>
+        <v>99878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104132</v>
+        <v>104140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>73981551</v>
       </c>
       <c r="B3" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>74084891</v>
       </c>
       <c r="B4" t="n">
-        <v>99878</v>
+        <v>99888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104140</v>
+        <v>104150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>270124</v>
+        <v>79900</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,17 +703,26 @@
           <t>(Lange) Holub</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ropudden, 1000 m N om, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549596.0034283608</v>
+        <v>549596</v>
       </c>
       <c r="R2" t="n">
-        <v>6408227.928815917</v>
+        <v>6408228</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -743,24 +747,19 @@
           <t>Djursdala</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-Hf-Vim-0012</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-12-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,11 +771,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Längs källdrag i gran-hasselskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -790,51 +784,51 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73981551</v>
+        <v>74084891</v>
       </c>
       <c r="B3" t="n">
-        <v>109264</v>
+        <v>100346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>174</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>L6 Andersberg, Sm</t>
+          <t>Ropudden 1000 m N, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549788</v>
+        <v>549591</v>
       </c>
       <c r="R3" t="n">
-        <v>6408425</v>
+        <v>6408223</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -861,17 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1985-12-31</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G2a 0019. SOM: Hypochoeris maculata. LEG: Erik Moberger</t>
+          <t>Smålands flora 2007: KOO: 7G1a 4817. SOM: Bromopsis benekenii. LEG: Sören Mjösberg. KOM: Det. BD ThK</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +879,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äng</t>
+          <t>Längs källdrag i gran-hasselskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,45 +901,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74084891</v>
+        <v>73981551</v>
       </c>
       <c r="B4" t="n">
-        <v>99888</v>
+        <v>109814</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>174</v>
+        <v>220204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ropudden 1000 m N, Sm</t>
+          <t>L6 Andersberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549591</v>
+        <v>549788</v>
       </c>
       <c r="R4" t="n">
-        <v>6408223</v>
+        <v>6408425</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,17 +966,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
+          <t>1985-12-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G1a 4817. SOM: Bromopsis benekenii. LEG: Sören Mjösberg. KOM: Det. BD ThK</t>
+          <t>Smålands flora 2007: KOO: 7G2a 0019. SOM: Hypochoeris maculata. LEG: Erik Moberger</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +990,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Längs källdrag i gran-hasselskog</t>
+          <t>Äng</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1021,7 +1015,7 @@
         <v>74462991</v>
       </c>
       <c r="B5" t="n">
-        <v>104150</v>
+        <v>104640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15427-2023 artfynd.xlsx
+++ b/artfynd/A 15427-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79900</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74084891</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73981551</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74462991</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>